--- a/rally_skill_test_cases_talisman.xlsx
+++ b/rally_skill_test_cases_talisman.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/azizalam/Claude/Skills/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15733E50-F91C-5F4E-8234-93063E2D897A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EFD791-4926-FF47-A9A6-070484CBE46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Rally Skill Tests" sheetId="1" r:id="rId1"/>
+    <sheet name="Rally create ticket Skill Tests" sheetId="1" r:id="rId1"/>
+    <sheet name="AskVsAssume" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rally Skill Tests'!$A$1:$J$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rally create ticket Skill Tests'!$A$1:$J$17</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="156">
   <si>
     <t>Test ID</t>
   </si>
@@ -193,63 +194,18 @@
     <t>TC-08</t>
   </si>
   <si>
-    <t>Story with Child Tasks</t>
-  </si>
-  <si>
-    <t>We need Data Lake ingestion for the Claims feed. Daily files should land in the raw zone, and failed loads should raise an alert. Create the story with three tasks: design the landing-zone schema (3 hours, architect), build the SSIS ingestion package (5 hours, dev), and write reconciliation tests (2 hours, qa).</t>
-  </si>
-  <si>
-    <t>Rally skill loaded; users architect, dev and qa exist</t>
-  </si>
-  <si>
-    <t>Paste Prompt 8 → run skill → open Rally and verify</t>
-  </si>
-  <si>
-    <t>One Story (title inferred, e.g. Data Lake ingestion for Claims feed) with Acceptance Criteria: daily files land in raw zone; failed loads raise an alert + 3 child Tasks: Design landing-zone schema (Est 3, architect), Build SSIS ingestion package (Est 5, dev), Write reconciliation tests (Est 2, qa)</t>
-  </si>
-  <si>
-    <t>Acceptance Criteria must be extracted from the second sentence</t>
-  </si>
-  <si>
     <t>TC-09</t>
   </si>
   <si>
-    <t>Hierarchy (Validation)</t>
-  </si>
-  <si>
-    <t>Story with Child Defects</t>
-  </si>
-  <si>
-    <t>Create a story for refactoring the Premium mart. Two defects have already come out of it, so add them under the story: currency conversion is wrong for non-GBP policies (medium), and the calendar dimension is missing 2027 dates (low).</t>
-  </si>
-  <si>
     <t>Rally skill loaded</t>
   </si>
   <si>
-    <t>Paste Prompt 9 → run skill → open Rally and verify</t>
-  </si>
-  <si>
-    <t>One Story (title inferred, e.g. Premium mart refactor) + 2 child Defects: currency conversion wrong for non-GBP policies (Priority=Medium) and calendar dimension missing 2027 dates (Priority=Low)</t>
-  </si>
-  <si>
-    <t>Validation pattern: not typical daily workflow</t>
-  </si>
-  <si>
     <t>TC-10</t>
   </si>
   <si>
-    <t>Story with Tasks + Defects</t>
-  </si>
-  <si>
-    <t>Create a story for incremental loading of the Claims mart. It needs two tasks: add watermark logic to the SSIS Claims package (8 hours, dev1) and update the usp_LoadClaimsMart merge logic (3 hours, dev2). Also log a high priority defect under it: duplicate claim rows appear when the incremental load is rerun.</t>
-  </si>
-  <si>
     <t>Paste Prompt 10 → run skill → open Rally and verify</t>
   </si>
   <si>
-    <t>One Story (title inferred, e.g. Incremental load for Claims mart) + 2 Tasks (Est 8 dev1; Est 3 dev2) + 1 Defect (Priority=High; duplicate claim rows on rerun), all parented to the Story</t>
-  </si>
-  <si>
     <t>Check both Tasks and Defects tabs</t>
   </si>
   <si>
@@ -370,9 +326,6 @@
     <t>Hallucination risk</t>
   </si>
   <si>
-    <t>TC-17</t>
-  </si>
-  <si>
     <t>Unknown Parent Reference</t>
   </si>
   <si>
@@ -391,9 +344,6 @@
     <t>High-risk: data integrity</t>
   </si>
   <si>
-    <t>TC-18</t>
-  </si>
-  <si>
     <t>Missing Attachment</t>
   </si>
   <si>
@@ -428,13 +378,182 @@
   </si>
   <si>
     <t>One Task; title inferred (e.g. Add null check to usp_LoadClaimsStaging); Description mentions missing claim reference; Parent=DE5678; Estimate=2; Owner=Aziz Alam</t>
+  </si>
+  <si>
+    <t>Situation</t>
+  </si>
+  <si>
+    <t>Skill Should…</t>
+  </si>
+  <si>
+    <t>Rationale</t>
+  </si>
+  <si>
+    <t>Unknown parent Formatted ID</t>
+  </si>
+  <si>
+    <t>ASK / REPORT</t>
+  </si>
+  <si>
+    <t>Do not create orphaned tickets</t>
+  </si>
+  <si>
+    <t>Missing required fields (if Rally workspace requires them)</t>
+  </si>
+  <si>
+    <t>ASK</t>
+  </si>
+  <si>
+    <t>Avoid violating process with guessed defaults</t>
+  </si>
+  <si>
+    <t>Defect parenting in a batch prompt</t>
+  </si>
+  <si>
+    <t>Rally supports both standalone and parented defects</t>
+  </si>
+  <si>
+    <t>Attachment file not found</t>
+  </si>
+  <si>
+    <t>REPORT &amp; CONTINUE</t>
+  </si>
+  <si>
+    <t>Do not abort the entire ticket</t>
+  </si>
+  <si>
+    <t>Project not specified</t>
+  </si>
+  <si>
+    <t>Standard config behavior</t>
+  </si>
+  <si>
+    <t>Priority/Severity not specified</t>
+  </si>
+  <si>
+    <t>Otherwise leave blank and report</t>
+  </si>
+  <si>
+    <t>Owner not specified</t>
+  </si>
+  <si>
+    <t>Rally allows unassigned</t>
+  </si>
+  <si>
+    <t>Tags not specified</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>Task parent in prompt</t>
+  </si>
+  <si>
+    <t>Matches natural workflow</t>
+  </si>
+  <si>
+    <t>Referenced Formatted ID exists</t>
+  </si>
+  <si>
+    <t>NEVER ASSUME</t>
+  </si>
+  <si>
+    <t>Always verify</t>
+  </si>
+  <si>
+    <t>Attachment path is valid</t>
+  </si>
+  <si>
+    <t>Always check</t>
+  </si>
+  <si>
+    <t>Vague description maps to known issue</t>
+  </si>
+  <si>
+    <r>
+      <t>ASSUME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> Rally default</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ASSUME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> unassigned</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ASSUME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> empty</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ASSUME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> most recently referenced Story/Defect</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ASSUME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> default Project</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a story for incremental loading of the Claims mart. It needs two tasks: add watermark logic to the SSIS Claims package (8 hours, dev1) and update the usp_LoadClaimsMart merge logic (3 hours, dev2). </t>
+  </si>
+  <si>
+    <t>Story with Tasks</t>
+  </si>
+  <si>
+    <t>One Story (title inferred, e.g. Incremental load for Claims mart) + 2 Tasks (Est 8 dev1; Est 3 dev2)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -453,6 +572,18 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FF0F1115"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -478,16 +609,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -841,7 +972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -929,7 +1060,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>21</v>
@@ -938,7 +1069,7 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="2" t="s">
@@ -959,7 +1090,7 @@
         <v>26</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>27</v>
@@ -968,7 +1099,7 @@
         <v>28</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="2" t="s">
@@ -978,7 +1109,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
@@ -989,7 +1120,7 @@
         <v>31</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>32</v>
@@ -998,7 +1129,7 @@
         <v>33</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="2" t="s">
@@ -1064,7 +1195,7 @@
       </c>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>48</v>
       </c>
@@ -1092,7 +1223,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:10" ht="70" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="42" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>55</v>
       </c>
@@ -1100,327 +1231,268 @@
         <v>49</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>59</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="56" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="53" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="70" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:10" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="42" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" ht="70" x14ac:dyDescent="0.2">
+      <c r="J12" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" ht="56" x14ac:dyDescent="0.2">
+      <c r="J13" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="42" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="E14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J14" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="28" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="56" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J15" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="28" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="42" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J16" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="28" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="F17" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="28" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="42" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J19" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="I2:I19">
+  <autoFilter ref="A1:J17" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
@@ -1435,10 +1507,168 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" errorTitle="Invalid status" error="Choose Pass, Fail, Blocked, Not Run or N/A" sqref="I2:I19" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" errorTitle="Invalid status" error="Choose Pass, Fail, Blocked, Not Run or N/A" sqref="I2:I17" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Pass,Fail,Blocked,Not Run,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A11CC1F1-6FE5-9F4E-9828-393E80302A93}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="66" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>